--- a/data/trans_camb/P62-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P62-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,22</t>
+          <t>-0,29; 2,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 3,16</t>
+          <t>0,01; 2,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 3,01</t>
+          <t>-0,58; 2,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,84</t>
+          <t>0,85; 5,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,09</t>
+          <t>1,4; 6,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,88</t>
+          <t>0,0; 6,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,88</t>
+          <t>0,56; 2,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,75</t>
+          <t>1,02; 3,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 3,17</t>
+          <t>-0,01; 2,93</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,4; —</t>
+          <t>39,23; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>102,15; —</t>
+          <t>103,63; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 5,48</t>
+          <t>-2,08; 5,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 6,38</t>
+          <t>-2,15; 6,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 19,5</t>
+          <t>0,34; 20,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 7,87</t>
+          <t>0,5; 8,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 4,29</t>
+          <t>-2,57; 4,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 9,78</t>
+          <t>-0,58; 9,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 5,66</t>
+          <t>0,18; 5,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,82</t>
+          <t>-1,08; 4,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 10,79</t>
+          <t>1,01; 10,47</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-40,84; 381,45</t>
+          <t>-40,34; 404,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,59; 378,31</t>
+          <t>-46,02; 355,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,58; 1032,31</t>
+          <t>-15,21; 984,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 348,37</t>
+          <t>0,9; 370,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,52; 202,12</t>
+          <t>-52,95; 192,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 447,69</t>
+          <t>-24,69; 396,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 230,52</t>
+          <t>-2,67; 242,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,88; 150,09</t>
+          <t>-23,05; 194,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,7; 435,01</t>
+          <t>10,61; 365,08</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-30,7; -4,41</t>
+          <t>-31,44; -5,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-35,11; -9,53</t>
+          <t>-34,63; -10,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-24,79; 6,48</t>
+          <t>-24,48; 7,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 9,02</t>
+          <t>0,98; 8,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 7,63</t>
+          <t>0,08; 7,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,56; 13,89</t>
+          <t>4,74; 14,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 7,12</t>
+          <t>-1,12; 6,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 4,84</t>
+          <t>-3,19; 4,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,1; 13,02</t>
+          <t>2,77; 13,21</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-66,23; -16,55</t>
+          <t>-67,64; -18,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-75,48; -35,67</t>
+          <t>-75,94; -38,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-57,12; 23,49</t>
+          <t>-57,03; 29,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,04; 241,29</t>
+          <t>11,34; 260,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,05; 228,52</t>
+          <t>-0,4; 228,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67,98; 424,29</t>
+          <t>67,76; 404,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 91,0</t>
+          <t>-8,9; 93,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,43; 63,1</t>
+          <t>-26,62; 58,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,46; 162,36</t>
+          <t>23,2; 162,99</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-37,84; -12,11</t>
+          <t>-38,53; -12,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-39,88; -14,69</t>
+          <t>-40,72; -15,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-29,88; -1,23</t>
+          <t>-31,42; -2,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 7,33</t>
+          <t>-2,34; 7,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 5,02</t>
+          <t>-4,71; 4,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 8,94</t>
+          <t>-0,86; 9,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 5,31</t>
+          <t>-4,76; 5,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 3,59</t>
+          <t>-6,48; 3,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 9,88</t>
+          <t>-1,86; 9,68</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-59,25; -26,82</t>
+          <t>-58,45; -25,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-61,06; -31,41</t>
+          <t>-61,92; -31,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-47,03; -4,68</t>
+          <t>-47,78; -4,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,44; 75,48</t>
+          <t>-16,67; 81,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,01; 55,03</t>
+          <t>-32,97; 50,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 98,99</t>
+          <t>-5,96; 96,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,94; 31,09</t>
+          <t>-20,98; 32,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,21; 20,29</t>
+          <t>-27,83; 20,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 56,1</t>
+          <t>-8,01; 53,21</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-20,67; -4,37</t>
+          <t>-20,51; -3,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-21,12; -4,53</t>
+          <t>-21,02; -5,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,5; -4,37</t>
+          <t>-20,19; -5,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 8,04</t>
+          <t>-5,26; 8,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 12,07</t>
+          <t>-1,54; 12,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,93; 13,69</t>
+          <t>1,52; 13,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 2,35</t>
+          <t>-9,11; 2,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 5,42</t>
+          <t>-5,6; 5,94</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 6,16</t>
+          <t>-4,67; 6,39</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-25,91; -6,06</t>
+          <t>-25,57; -5,21</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-26,1; -6,26</t>
+          <t>-26,11; -7,78</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-24,44; -6,74</t>
+          <t>-25,13; -7,21</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-18,54; 37,37</t>
+          <t>-20,08; 38,05</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 56,87</t>
+          <t>-5,27; 58,33</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,96; 65,31</t>
+          <t>5,26; 64,75</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-19,25; 5,59</t>
+          <t>-18,78; 4,98</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 12,73</t>
+          <t>-11,44; 14,31</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 14,75</t>
+          <t>-9,63; 15,07</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 2,76</t>
+          <t>-0,15; 2,87</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,73</t>
+          <t>-1,83; 1,81</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-16,69; -10,23</t>
+          <t>-16,62; -10,11</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,09; 20,08</t>
+          <t>5,52; 19,42</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,58; 18,79</t>
+          <t>3,45; 18,86</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,83; 40,57</t>
+          <t>4,86; 39,73</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,13; 12,22</t>
+          <t>2,94; 12,1</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2,03; 10,61</t>
+          <t>1,87; 11,03</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 16,11</t>
+          <t>-3,67; 17,53</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 2,83</t>
+          <t>-0,15; 2,97</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 1,78</t>
+          <t>-1,84; 1,87</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-16,85; -10,46</t>
+          <t>-16,84; -10,28</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9,15; 41,78</t>
+          <t>10,05; 40,74</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8,5; 40,17</t>
+          <t>6,38; 39,27</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,14; 84,26</t>
+          <t>9,06; 87,99</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,12; 17,29</t>
+          <t>3,85; 17,07</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2,7; 15,09</t>
+          <t>2,5; 15,56</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 22,52</t>
+          <t>-4,89; 24,5</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,0</t>
+          <t>-0,85; 1,68</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,62</t>
+          <t>-1,36; 1,36</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-15,02; -8,26</t>
+          <t>-15,26; -8,62</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 9,86</t>
+          <t>-3,71; 9,75</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 7,92</t>
+          <t>-7,26; 6,29</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 7,29</t>
+          <t>-4,78; 7,14</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 6,13</t>
+          <t>-2,15; 6,61</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 4,83</t>
+          <t>-4,18; 5,01</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 0,4</t>
+          <t>-7,32; 0,64</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,04</t>
+          <t>-0,85; 1,72</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,65</t>
+          <t>-1,36; 1,38</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-15,04; -8,37</t>
+          <t>-15,32; -8,69</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 14,21</t>
+          <t>-4,69; 13,68</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 11,1</t>
+          <t>-9,47; 8,83</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 10,49</t>
+          <t>-6,04; 10,1</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 7,54</t>
+          <t>-2,48; 8,12</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 5,92</t>
+          <t>-4,79; 6,18</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 0,49</t>
+          <t>-8,58; 0,77</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-14,1; -6,94</t>
+          <t>-13,86; -6,97</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-11,59; -4,86</t>
+          <t>-11,88; -4,67</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 3,51</t>
+          <t>-4,89; 3,51</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,89</t>
+          <t>1,76; 6,79</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,81; 8,16</t>
+          <t>2,92; 8,33</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11,97; 36,22</t>
+          <t>11,92; 35,15</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 2,3</t>
+          <t>-2,16; 2,1</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 4,1</t>
+          <t>-0,45; 3,74</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>8,14; 23,3</t>
+          <t>8,18; 21,92</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-25,03; -13,3</t>
+          <t>-24,7; -13,3</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-20,64; -9,42</t>
+          <t>-21,02; -8,86</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 6,66</t>
+          <t>-8,49; 6,65</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7,01; 29,37</t>
+          <t>6,64; 29,12</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>10,56; 34,94</t>
+          <t>10,92; 35,62</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>47,7; 142,68</t>
+          <t>46,95; 147,57</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 6,69</t>
+          <t>-5,9; 6,14</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 11,75</t>
+          <t>-1,24; 10,83</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>22,51; 65,35</t>
+          <t>22,54; 60,62</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P62-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P62-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,12</t>
+          <t>1,72</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>0,96</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 2,16</t>
+          <t>-0,3; 2,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,01; 2,99</t>
+          <t>0,0; 3,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 2,67</t>
+          <t>-0,59; 2,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,09</t>
+          <t>0,89; 5,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 6,07</t>
+          <t>1,66; 6,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,22</t>
+          <t>0,0; 5,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,97</t>
+          <t>0,64; 2,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,67</t>
+          <t>0,96; 3,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 2,93</t>
+          <t>-0,04; 2,81</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>120,74%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>694,14%</t>
+          <t>563,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>368,15%</t>
+          <t>320,84%</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,23; —</t>
+          <t>27,91; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>103,63; —</t>
+          <t>62,29; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,71</t>
+          <t>6,89</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,81</t>
+          <t>3,43</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>4,5</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 5,76</t>
+          <t>-2,51; 5,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 6,11</t>
+          <t>-1,73; 6,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 20,13</t>
+          <t>0,19; 17,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 8,18</t>
+          <t>-0,12; 7,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 4,15</t>
+          <t>-2,99; 3,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 9,18</t>
+          <t>-0,72; 9,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 5,67</t>
+          <t>0,16; 5,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 4,16</t>
+          <t>-1,27; 4,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 10,47</t>
+          <t>0,92; 9,38</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>214,45%</t>
+          <t>191,54%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>100,28%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>135,43%</t>
+          <t>121,0%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-40,34; 404,32</t>
+          <t>-43,92; 324,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-46,02; 355,52</t>
+          <t>-35,58; 398,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 984,08</t>
+          <t>-22,97; 953,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 370,5</t>
+          <t>-12,66; 327,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,95; 192,08</t>
+          <t>-57,0; 150,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,69; 396,41</t>
+          <t>-21,69; 364,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 242,79</t>
+          <t>-1,15; 242,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 194,87</t>
+          <t>-26,85; 174,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,61; 365,08</t>
+          <t>14,52; 352,85</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-8,41</t>
+          <t>-10,0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,0</t>
+          <t>7,88</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,98</t>
+          <t>6,59</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-31,44; -5,18</t>
+          <t>-30,5; -4,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-34,63; -10,06</t>
+          <t>-34,28; -9,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-24,48; 7,35</t>
+          <t>-25,36; 5,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,6</t>
+          <t>0,89; 8,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 7,42</t>
+          <t>0,14; 7,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,74; 14,04</t>
+          <t>3,67; 12,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 6,77</t>
+          <t>-1,1; 7,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 4,42</t>
+          <t>-3,1; 5,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 13,21</t>
+          <t>1,84; 11,26</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-23,38%</t>
+          <t>-27,78%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>179,42%</t>
+          <t>157,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>67,45%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-67,64; -18,63</t>
+          <t>-66,75; -14,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-75,94; -38,47</t>
+          <t>-74,82; -35,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-57,03; 29,7</t>
+          <t>-56,23; 22,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,34; 260,79</t>
+          <t>12,92; 249,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 228,19</t>
+          <t>1,03; 209,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67,76; 404,07</t>
+          <t>57,88; 361,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 93,34</t>
+          <t>-10,12; 93,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,62; 58,42</t>
+          <t>-26,96; 68,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,2; 162,99</t>
+          <t>15,86; 143,97</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-16,44</t>
+          <t>-16,23</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,17</t>
+          <t>4,63</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>4,49</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-38,53; -12,58</t>
+          <t>-38,13; -13,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-40,72; -15,72</t>
+          <t>-39,82; -15,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-31,42; -2,35</t>
+          <t>-30,49; -1,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 7,66</t>
+          <t>-2,73; 7,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 4,73</t>
+          <t>-4,54; 4,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 9,02</t>
+          <t>-0,32; 9,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 5,64</t>
+          <t>-4,83; 5,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 3,66</t>
+          <t>-6,64; 3,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 9,68</t>
+          <t>-0,88; 10,68</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-29,01%</t>
+          <t>-28,65%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-58,45; -25,81</t>
+          <t>-58,16; -27,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-61,92; -31,2</t>
+          <t>-61,63; -33,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-47,78; -4,72</t>
+          <t>-46,47; -3,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 81,93</t>
+          <t>-18,72; 85,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,97; 50,63</t>
+          <t>-31,26; 53,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 96,57</t>
+          <t>-2,07; 101,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-20,98; 32,14</t>
+          <t>-21,52; 31,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,83; 20,5</t>
+          <t>-28,26; 19,59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 53,21</t>
+          <t>-4,1; 61,41</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-12,5</t>
+          <t>-13,27</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,65</t>
+          <t>7,56</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>0,46</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-20,51; -3,74</t>
+          <t>-20,3; -4,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-21,02; -5,64</t>
+          <t>-21,38; -4,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,19; -5,29</t>
+          <t>-21,02; -5,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 8,01</t>
+          <t>-4,58; 8,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 12,06</t>
+          <t>-2,06; 11,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,52; 13,28</t>
+          <t>1,55; 13,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 2,15</t>
+          <t>-9,17; 2,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 5,94</t>
+          <t>-6,52; 5,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 6,39</t>
+          <t>-5,21; 5,67</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-16,07%</t>
+          <t>-17,06%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-25,57; -5,21</t>
+          <t>-24,81; -6,16</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-26,11; -7,78</t>
+          <t>-26,29; -6,6</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-25,13; -7,21</t>
+          <t>-25,89; -7,12</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,08; 38,05</t>
+          <t>-17,0; 39,45</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 58,33</t>
+          <t>-7,14; 55,34</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,26; 64,75</t>
+          <t>5,02; 66,39</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 4,98</t>
+          <t>-19,01; 6,29</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 14,31</t>
+          <t>-13,24; 12,39</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 15,07</t>
+          <t>-10,54; 13,35</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-13,22</t>
+          <t>-13,03</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>7,54</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>-1,43</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 2,87</t>
+          <t>-0,12; 3,07</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,81</t>
+          <t>-1,87; 1,84</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-16,62; -10,11</t>
+          <t>-16,22; -9,58</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,52; 19,42</t>
+          <t>5,34; 19,52</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,45; 18,86</t>
+          <t>4,16; 19,04</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,86; 39,73</t>
+          <t>1,04; 13,22</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,94; 12,1</t>
+          <t>2,93; 11,96</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,87; 11,03</t>
+          <t>2,17; 11,23</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 17,53</t>
+          <t>-5,6; 2,69</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-13,43%</t>
+          <t>-13,22%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>-1,95%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 2,97</t>
+          <t>-0,11; 3,17</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,87</t>
+          <t>-1,89; 1,89</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-16,84; -10,28</t>
+          <t>-16,42; -9,87</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10,05; 40,74</t>
+          <t>10,1; 40,57</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>6,38; 39,27</t>
+          <t>7,48; 39,4</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,06; 87,99</t>
+          <t>2,27; 28,0</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,85; 17,07</t>
+          <t>4,03; 17,08</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2,5; 15,56</t>
+          <t>2,84; 15,84</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 24,5</t>
+          <t>-7,41; 3,83</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-11,59</t>
+          <t>-11,4</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>1,43</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-3,59</t>
+          <t>-3,3</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,68</t>
+          <t>-0,86; 1,59</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,36</t>
+          <t>-1,37; 1,16</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-15,26; -8,62</t>
+          <t>-14,54; -8,29</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 9,75</t>
+          <t>-4,09; 9,51</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 6,29</t>
+          <t>-6,62; 7,16</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 7,14</t>
+          <t>-4,13; 7,17</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 6,61</t>
+          <t>-2,3; 6,56</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 5,01</t>
+          <t>-4,19; 4,82</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 0,64</t>
+          <t>-7,16; 0,74</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-11,65%</t>
+          <t>-11,46%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-4,27%</t>
+          <t>-3,93%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,72</t>
+          <t>-0,86; 1,63</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,38</t>
+          <t>-1,36; 1,18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-15,32; -8,69</t>
+          <t>-14,61; -8,41</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 13,68</t>
+          <t>-5,22; 13,68</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 8,83</t>
+          <t>-8,6; 10,42</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 10,1</t>
+          <t>-5,24; 10,19</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 8,12</t>
+          <t>-2,63; 8,11</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 6,18</t>
+          <t>-4,77; 5,92</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 0,77</t>
+          <t>-8,28; 1,0</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,66</t>
+          <t>12,21</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>12,07</t>
+          <t>8,9</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-13,86; -6,97</t>
+          <t>-13,98; -7,08</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-11,88; -4,67</t>
+          <t>-11,52; -4,76</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 3,51</t>
+          <t>-3,29; 4,53</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,76; 6,79</t>
+          <t>1,65; 6,94</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,92; 8,33</t>
+          <t>2,85; 8,19</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11,92; 35,15</t>
+          <t>9,73; 14,76</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,1</t>
+          <t>-2,15; 2,12</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 3,74</t>
+          <t>-0,38; 3,74</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>8,18; 21,92</t>
+          <t>6,78; 11,0</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-0,78%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-24,7; -13,3</t>
+          <t>-24,68; -13,44</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-21,02; -8,86</t>
+          <t>-20,6; -9,21</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 6,65</t>
+          <t>-5,85; 8,69</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6,64; 29,12</t>
+          <t>6,35; 29,67</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>10,92; 35,62</t>
+          <t>11,08; 35,38</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>46,95; 147,57</t>
+          <t>37,59; 64,33</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 6,14</t>
+          <t>-5,88; 6,18</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 10,83</t>
+          <t>-1,03; 10,69</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>22,54; 60,62</t>
+          <t>18,14; 31,7</t>
         </is>
       </c>
     </row>
